--- a/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infection\Infection\Assets\ExcelData\UnitStatsData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E88891-95C4-42A9-BC02-48C2A6AEA3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C5AF6-74DF-425F-85C2-0D2E6ACF3F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitParameter" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>unitCode</t>
     <phoneticPr fontId="1"/>
@@ -79,50 +79,71 @@
     <t>Attacker</t>
   </si>
   <si>
+    <t>Healer</t>
+  </si>
+  <si>
+    <t>AtkBoost</t>
+  </si>
+  <si>
+    <t>SpdBoost</t>
+  </si>
+  <si>
+    <t>Regeneration</t>
+  </si>
+  <si>
+    <t>unitName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アタッカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タンカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒーラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>virusPow</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>leaderSkill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maxHp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>virusPoint</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>virusMaxPoint</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enemyVirusPoint</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enemyVirusMaxPoint</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maxLv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Tank</t>
-  </si>
-  <si>
-    <t>Healer</t>
-  </si>
-  <si>
-    <t>AtkBoost</t>
-  </si>
-  <si>
-    <t>SpdBoost</t>
-  </si>
-  <si>
-    <t>Regeneration</t>
-  </si>
-  <si>
-    <t>unitName</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アタッカー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タンカー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒーラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>virusPow</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>leaderSkill</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>role</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>virusHp</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -487,73 +508,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F54A597-E5C2-440A-A3B1-9CF5CE557CE3}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.375" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="13" max="14" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.75" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="11" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="9.625" customWidth="1"/>
+    <col min="15" max="15" width="10.625" customWidth="1"/>
+    <col min="17" max="17" width="7" customWidth="1"/>
+    <col min="18" max="18" width="14.625" customWidth="1"/>
+    <col min="20" max="20" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" t="s">
+      <c r="T1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -562,127 +605,172 @@
         <v>1</v>
       </c>
       <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="M2">
         <v>30</v>
       </c>
-      <c r="I2">
+      <c r="N2">
         <v>15</v>
       </c>
-      <c r="J2">
+      <c r="O2">
         <v>3</v>
       </c>
-      <c r="K2">
+      <c r="P2">
         <v>12</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-      <c r="N2">
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>10</v>
+      </c>
+      <c r="S2">
         <v>3</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10002</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>100</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>100</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
         <v>7</v>
       </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3">
         <v>5</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-      <c r="N3">
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>10</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="O3">
+      <c r="T3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>10003</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>30</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4">
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
         <v>6</v>
       </c>
-      <c r="K4">
+      <c r="P4">
         <v>7</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>10</v>
+      </c>
+      <c r="S4">
         <v>3</v>
       </c>
-      <c r="O4">
+      <c r="T4">
         <v>10</v>
       </c>
     </row>

--- a/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infection\Infection\Assets\ExcelData\UnitStatsData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C5AF6-74DF-425F-85C2-0D2E6ACF3F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143CE001-6553-4686-8B37-AEF4725DB74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitParameter" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>unitCode</t>
     <phoneticPr fontId="1"/>
@@ -144,6 +144,13 @@
   </si>
   <si>
     <t>Tank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>アーチャー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -508,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F54A597-E5C2-440A-A3B1-9CF5CE557CE3}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -774,11 +781,73 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>10004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>6</v>
+      </c>
+      <c r="P5">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{17471DB3-2646-4570-B79A-A51A225BA179}">
-      <formula1>"Attacker,Tank,Healer,Baffer,Debuffer"</formula1>
+      <formula1>"Attacker,Tank,Healer,Baffer,Debuffer,Archer"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{87ED1714-739D-478F-A37B-768193FB1AF9}">
       <formula1>"AtkBoost,SpdBoost,Regeneration"</formula1>

--- a/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infection\Infection\Assets\ExcelData\UnitStatsData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143CE001-6553-4686-8B37-AEF4725DB74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1C1B5C-C584-4744-A956-5711109F5F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>unitCode</t>
     <phoneticPr fontId="1"/>
@@ -152,6 +152,13 @@
   <si>
     <t>アーチャー</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウィザード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wizard</t>
   </si>
 </sst>
 </file>
@@ -515,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F54A597-E5C2-440A-A3B1-9CF5CE557CE3}">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -822,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -840,6 +847,68 @@
         <v>3</v>
       </c>
       <c r="T5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>10005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>10</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
         <v>10</v>
       </c>
     </row>
@@ -847,7 +916,7 @@
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{17471DB3-2646-4570-B79A-A51A225BA179}">
-      <formula1>"Attacker,Tank,Healer,Baffer,Debuffer,Archer"</formula1>
+      <formula1>"Attacker,Tank,Healer,Baffer,Debuffer,Archer,Wizard"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{87ED1714-739D-478F-A37B-768193FB1AF9}">
       <formula1>"AtkBoost,SpdBoost,Regeneration"</formula1>

--- a/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infection\Infection\Assets\ExcelData\UnitStatsData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1C1B5C-C584-4744-A956-5711109F5F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641CA409-DB3E-45C3-BE38-92FA82846312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitParameter" sheetId="1" r:id="rId1"/>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S2">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S3">
         <v>3</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <v>3</v>

--- a/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infection\Infection\Assets\ExcelData\UnitStatsData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641CA409-DB3E-45C3-BE38-92FA82846312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D00CB92-13AA-4D0E-A459-AAAF0E8DB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitParameter" sheetId="1" r:id="rId1"/>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>3</v>
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>3</v>

--- a/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/UnitStatsData/UnitStatsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infection\Infection\Assets\ExcelData\UnitStatsData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D00CB92-13AA-4D0E-A459-AAAF0E8DB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F31E98-10C2-4215-AE54-A9679E55D7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B387F37B-A662-40EF-8D8D-0E1E48D0E98C}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitParameter" sheetId="1" r:id="rId1"/>
@@ -640,7 +640,7 @@
         <v>100</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N2">
         <v>15</v>
@@ -649,7 +649,7 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -711,7 +711,7 @@
         <v>10</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>10</v>
@@ -773,7 +773,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -835,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
